--- a/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Technical Specification Template.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Technical Specification Template.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="192">
   <si>
-    <t xml:space="preserve">FOLIO — Ficha técnica editable de vitola (a completar con el torcedor y la fábrica)</t>
+    <t xml:space="preserve">ARNALDO — Ficha técnica editable de vitola (a completar con el torcedor y la fábrica)</t>
   </si>
   <si>
     <t xml:space="preserve">No contiene recetas ni ligas inventadas. Campos 'Valor' en azul = a rellenar. Rangos marcados 'orientativo' deben validarse con la fábrica.</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Nombre de vitola comercial</t>
   </si>
   <si>
-    <t xml:space="preserve">OCTAVO (inicial)</t>
+    <t xml:space="preserve">ARNALDO Nº 1 (inicial)</t>
   </si>
   <si>
     <t xml:space="preserve">Marca</t>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Unidades por caja / tipo de caja / anilla / pie de anilla</t>
   </si>
   <si>
-    <t xml:space="preserve">10 u · cedro · anilla FOLIO + pie 'Pliego Nº'</t>
+    <t xml:space="preserve">10 u · cedro · anilla ARNALDO (firma) + pie 'Pliego Nº'</t>
   </si>
   <si>
     <t xml:space="preserve">Colofón numerado incluido</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Una vitola de lanzamiento; extensiones sólo tras validar consistencia y venta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre FOLIO</t>
+    <t xml:space="preserve">Nombre ARNALDO</t>
   </si>
   <si>
     <t xml:space="preserve">Vitola de referencia</t>
@@ -261,7 +261,7 @@
     <t xml:space="preserve">Complejidad</t>
   </si>
   <si>
-    <t xml:space="preserve">OCTAVO</t>
+    <t xml:space="preserve">Nº 1</t>
   </si>
   <si>
     <t xml:space="preserve">Robusto</t>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">Media</t>
   </si>
   <si>
-    <t xml:space="preserve">CUARTO</t>
+    <t xml:space="preserve">Nº 2</t>
   </si>
   <si>
     <t xml:space="preserve">Toro / Gordito</t>
@@ -297,7 +297,7 @@
     <t xml:space="preserve">Media-alta</t>
   </si>
   <si>
-    <t xml:space="preserve">IMPERIAL</t>
+    <t xml:space="preserve">Nº 3</t>
   </si>
   <si>
     <t xml:space="preserve">Churchill (Julieta No. 2)</t>
@@ -1551,7 +1551,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>72</v>
       </c>

--- a/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Technical Specification Template.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/01_BRAND/Technical Specification Template.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="192">
   <si>
-    <t xml:space="preserve">ARNALDO — Ficha técnica editable de vitola (a completar con el torcedor y la fábrica)</t>
+    <t xml:space="preserve">ARNALDO VALLÉS — Ficha técnica editable de vitola (a completar con el torcedor y la fábrica)</t>
   </si>
   <si>
     <t xml:space="preserve">No contiene recetas ni ligas inventadas. Campos 'Valor' en azul = a rellenar. Rangos marcados 'orientativo' deben validarse con la fábrica.</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Nombre de vitola comercial</t>
   </si>
   <si>
-    <t xml:space="preserve">ARNALDO Nº 1 (inicial)</t>
+    <t xml:space="preserve">ARNALDO VALLÉS Nº 1 (inicial)</t>
   </si>
   <si>
     <t xml:space="preserve">Marca</t>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Unidades por caja / tipo de caja / anilla / pie de anilla</t>
   </si>
   <si>
-    <t xml:space="preserve">10 u · cedro · anilla ARNALDO (firma) + pie 'Pliego Nº'</t>
+    <t xml:space="preserve">10 u · cedro · anilla ARNALDO VALLÉS (firma) + pie 'Pliego Nº'</t>
   </si>
   <si>
     <t xml:space="preserve">Colofón numerado incluido</t>
@@ -243,7 +243,7 @@
     <t xml:space="preserve">Una vitola de lanzamiento; extensiones sólo tras validar consistencia y venta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre ARNALDO</t>
+    <t xml:space="preserve">Nombre ARNALDO VALLÉS</t>
   </si>
   <si>
     <t xml:space="preserve">Vitola de referencia</t>
@@ -1551,7 +1551,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>72</v>
       </c>
